--- a/learn-java-basic/src/main/resources/fast excel 着色后的结果.xlsx
+++ b/learn-java-basic/src/main/resources/fast excel 着色后的结果.xlsx
@@ -12,7 +12,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
+  <si>
+    <t>核验动作</t>
+  </si>
+  <si>
+    <t>核验项目</t>
+  </si>
+  <si>
+    <t>核验结果</t>
+  </si>
   <si>
     <t>运营输入标准</t>
   </si>
@@ -20,6 +29,46 @@
     <t>技术核验结果</t>
   </si>
   <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14.0"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>核验动作</t>
+    </r>
+  </si>
+  <si>
+    <t>有没有调</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12.0"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>有没有调</t>
+    </r>
+  </si>
+  <si>
+    <t>√</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <color rgb="FF00B400"/>
+        <sz val="18.0"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>√</t>
+    </r>
+  </si>
+  <si>
     <t>计划影响OD数量：1,329</t>
   </si>
   <si>
@@ -28,7 +77,7 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FFFF3232"/>
+        <color rgb="FF00B400"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -36,7 +85,7 @@
     </r>
   </si>
   <si>
-    <t>实际生效OD数量：890</t>
+    <t>实际生效OD数量：1,329</t>
   </si>
   <si>
     <r>
@@ -48,7 +97,46 @@
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
-      <t>890</t>
+      <t>1,329</t>
+    </r>
+  </si>
+  <si>
+    <t>测算覆盖变化 OD 数量(去重)：6,141
+测算覆盖变化 OD 数量(去重)/实际生效OD数：6,141/0=null%</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF000000"/>
+        <sz val="10.0"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>测算覆盖变化 OD 数量(去重)：6,141
+测算覆盖变化 OD 数量(去重)/实际生效OD数：6,141/0=null%</t>
+    </r>
+  </si>
+  <si>
+    <t>方向--有没有调对</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12.0"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>方向--有没有调对</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <color rgb="FFD18B0C"/>
+        <sz val="18.0"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>√</t>
     </r>
   </si>
   <si>
@@ -81,6 +169,44 @@
         <rFont val="宋体"/>
       </rPr>
       <t>-6.7%</t>
+    </r>
+  </si>
+  <si>
+    <t>产生少量降幅 占比:0.05%
+- 原因：调价前命中起步价兜底，老起步价兜底换标为真实起步价兜底，起步价兜底弹回普通里程
+- 分布：
+调降：7单
+平均降幅:-8.43%
+最大降幅:-18.09%
+最小降幅:-5.51%</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FFD18B0C"/>
+        <sz val="10.0"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>产生少量降幅 占比:0.05%
+- 原因：调价前命中起步价兜底，老起步价兜底换标为真实起步价兜底，起步价兜底弹回普通里程
+- 分布：
+调降：7单
+平均降幅:-8.43%
+最大降幅:-18.09%
+最小降幅:-5.51%</t>
+    </r>
+  </si>
+  <si>
+    <t>幅度--有没有调对</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12.0"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>幅度--有没有调对</t>
     </r>
   </si>
   <si>
@@ -161,7 +287,7 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FF00B400"/>
+        <color rgb="FF000000"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -172,7 +298,7 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FF00B400"/>
+        <color rgb="FF000000"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -183,7 +309,7 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FF00B400"/>
+        <color rgb="FF000000"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -218,7 +344,7 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FF00B400"/>
+        <color rgb="FF000000"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -229,7 +355,7 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FF00B400"/>
+        <color rgb="FF000000"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -240,7 +366,7 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FF00B400"/>
+        <color rgb="FF000000"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -275,7 +401,7 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FF00B400"/>
+        <color rgb="FF000000"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -286,7 +412,7 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FF00B400"/>
+        <color rgb="FF000000"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -297,7 +423,7 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FF00B400"/>
+        <color rgb="FF000000"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -332,7 +458,7 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FF00B400"/>
+        <color rgb="FF000000"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -343,7 +469,7 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FF00B400"/>
+        <color rgb="FF000000"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -354,7 +480,7 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FF00B400"/>
+        <color rgb="FF000000"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -380,7 +506,7 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FF00B400"/>
+        <color rgb="FFFF3232"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -505,6 +631,53 @@
         <rFont val="宋体"/>
       </rPr>
       <t>-6.3%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">由于统计周期导致单量偏差
+最大降幅：-27.273%
+最大降幅不一致原因：调价前命中起步价兜底，调价后命中真实起步价兜底，老起步价兜底换标为真实起步价兜底
+最小降幅：-0.015%
+最小降幅不一致原因：调价后命中单公里兜底
+降幅超过-20%, 数量:1, 占比:0.01%
+不一致率：572/14,405 = 3.97%
+-该调的没调（单量）：42
+-该调的没调（占比）：0.294%
+-降幅过大（单量）：9
+-降幅过大（占比）：0.065%
+-降幅过小（单量）：522
+-降幅过小（占比）：3.615%
+不一致原因：起步价兜底、单公里兜底
+</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">由于统计周期导致单量偏差
+最大降幅：-27.273%
+最大降幅不一致原因：调价前命中起步价兜底，调价后命中真实起步价兜底，老起步价兜底换标为真实起步价兜底
+最小降幅：-0.015%
+最小降幅不一致原因：调价后命中单公里兜底
+降幅超过-20%, 数量:1, 占比:0.01%
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD18B0C"/>
+        <sz val="10.0"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>不一致率：572/14,405 = 3.97%</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+-该调的没调（单量）：42
+-该调的没调（占比）：0.294%
+-降幅过大（单量）：9
+-降幅过大（占比）：0.065%
+-降幅过小（单量）：522
+-降幅过小（占比）：3.615%
+不一致原因：起步价兜底、单公里兜底
+</t>
     </r>
   </si>
 </sst>
@@ -513,7 +686,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="41">
+  <fonts count="53">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -528,17 +701,105 @@
     </font>
     <font>
       <name val="宋体"/>
+      <sz val="14.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="18.0"/>
+      <b val="true"/>
+      <color rgb="FF00B400"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF00B400"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF00B400"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="14.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="18.0"/>
+      <b val="true"/>
+      <color rgb="FFD18B0C"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FFD18B0C"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FFD18B0C"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FFD18B0C"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="14.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="18.0"/>
+      <b val="true"/>
+      <color rgb="FFD18B0C"/>
+    </font>
+    <font>
+      <name val="宋体"/>
       <sz val="10.0"/>
       <color rgb="FFFF3232"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <sz val="10.0"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FFFF3232"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF00B400"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FFFF3232"/>
     </font>
     <font>
       <name val="宋体"/>
@@ -548,16 +809,141 @@
     <font>
       <name val="宋体"/>
       <sz val="10.0"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF00B400"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FFFF3232"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF00B400"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF00B400"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FFFF3232"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF00B400"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FFFF3232"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FFFF3232"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF00B400"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FFFF3232"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
       <color rgb="FFD18B0C"/>
     </font>
     <font>
       <name val="宋体"/>
       <sz val="10.0"/>
+      <color rgb="FF00B400"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
       <color rgb="FFFF3232"/>
     </font>
     <font>
       <name val="宋体"/>
       <sz val="10.0"/>
+      <color rgb="FF00B400"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF00B400"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
       <color rgb="FFFF3232"/>
     </font>
     <font>
@@ -568,157 +954,7 @@
     <font>
       <name val="宋体"/>
       <sz val="10.0"/>
-      <color rgb="FFFF3232"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
       <color rgb="FFD18B0C"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FFFF3232"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FFFF3232"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FFFF3232"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FFFF3232"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FFD18B0C"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FFFF3232"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FFFF3232"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
     </font>
   </fonts>
   <fills count="4">
@@ -811,11 +1047,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyAlignment="true" applyBorder="true" applyFill="true" applyFont="true">
       <alignment horizontal="center" wrapText="true" vertical="center"/>
       <protection locked="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" wrapText="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="left" wrapText="true" vertical="top"/>
@@ -826,11 +1065,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="80.0" customWidth="true"/>
-    <col min="2" max="2" width="80.0" customWidth="true"/>
+    <col min="1" max="1" width="15.0" customWidth="true"/>
+    <col min="2" max="2" width="20.0" customWidth="true"/>
+    <col min="3" max="3" width="12.0" customWidth="true"/>
+    <col min="4" max="4" width="70.0" customWidth="true"/>
+    <col min="5" max="5" width="50.0" customWidth="true"/>
+    <col min="6" max="6" width="60.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -840,32 +1083,83 @@
       <c r="B1" t="s" s="1">
         <v>1</v>
       </c>
+      <c r="C1" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s" s="3">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s" s="3">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s" s="3">
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>9</v>
+        <v>18</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s" s="3">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s" s="3">
+        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="F4" t="s" s="3">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A4"/>
+  </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/learn-java-basic/src/main/resources/fast excel 着色后的结果.xlsx
+++ b/learn-java-basic/src/main/resources/fast excel 着色后的结果.xlsx
@@ -12,7 +12,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
+  <si>
+    <t>核验动作</t>
+  </si>
+  <si>
+    <t>核验项目</t>
+  </si>
+  <si>
+    <t>核验结果</t>
+  </si>
   <si>
     <t>运营输入标准</t>
   </si>
@@ -20,6 +29,46 @@
     <t>技术核验结果</t>
   </si>
   <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14.0"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>核验动作</t>
+    </r>
+  </si>
+  <si>
+    <t>有没有调</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12.0"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>有没有调</t>
+    </r>
+  </si>
+  <si>
+    <t>√</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <color rgb="FF00B400"/>
+        <sz val="18.0"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>√</t>
+    </r>
+  </si>
+  <si>
     <t>计划影响OD数量：1,329</t>
   </si>
   <si>
@@ -28,7 +77,7 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FFFF3232"/>
+        <color rgb="FF00B400"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -36,7 +85,7 @@
     </r>
   </si>
   <si>
-    <t>实际生效OD数量：890</t>
+    <t>实际生效OD数量：1,329</t>
   </si>
   <si>
     <r>
@@ -48,7 +97,46 @@
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
-      <t>890</t>
+      <t>1,329</t>
+    </r>
+  </si>
+  <si>
+    <t>测算覆盖变化 OD 数量(去重)：6,141
+测算覆盖变化 OD 数量(去重)/实际生效OD数：6,141/0=null%</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF000000"/>
+        <sz val="10.0"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>测算覆盖变化 OD 数量(去重)：6,141
+测算覆盖变化 OD 数量(去重)/实际生效OD数：6,141/0=null%</t>
+    </r>
+  </si>
+  <si>
+    <t>方向--有没有调对</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12.0"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>方向--有没有调对</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <color rgb="FFD18B0C"/>
+        <sz val="18.0"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>√</t>
     </r>
   </si>
   <si>
@@ -81,6 +169,44 @@
         <rFont val="宋体"/>
       </rPr>
       <t>-6.7%</t>
+    </r>
+  </si>
+  <si>
+    <t>产生少量降幅 占比:0.05%
+- 原因：调价前命中起步价兜底，老起步价兜底换标为真实起步价兜底，起步价兜底弹回普通里程
+- 分布：
+调降：7单
+平均降幅:-8.43%
+最大降幅:-18.09%
+最小降幅:-5.51%</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FFD18B0C"/>
+        <sz val="10.0"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>产生少量降幅 占比:0.05%
+- 原因：调价前命中起步价兜底，老起步价兜底换标为真实起步价兜底，起步价兜底弹回普通里程
+- 分布：
+调降：7单
+平均降幅:-8.43%
+最大降幅:-18.09%
+最小降幅:-5.51%</t>
+    </r>
+  </si>
+  <si>
+    <t>幅度--有没有调对</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12.0"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>幅度--有没有调对</t>
     </r>
   </si>
   <si>
@@ -94,7 +220,7 @@
 3、7米6：
 单量：154，调幅：-6.3%，快车响应率：92%，估转：46%，平均里程：86
 4、13米：
-单量：154，调幅：-6.3%，快车响应率：92%，估转：46%，平均里程：86</t>
+单量：154，调幅：-5%，快车响应率：92%，估转：46%，平均里程：86</t>
   </si>
   <si>
     <r>
@@ -161,7 +287,7 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FF00B400"/>
+        <color rgb="FF000000"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -172,7 +298,7 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FF00B400"/>
+        <color rgb="FF000000"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -183,7 +309,7 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FF00B400"/>
+        <color rgb="FF000000"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -218,7 +344,7 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FF00B400"/>
+        <color rgb="FF000000"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -229,7 +355,7 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FF00B400"/>
+        <color rgb="FF000000"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -240,7 +366,7 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FF00B400"/>
+        <color rgb="FF000000"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -275,7 +401,7 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FF00B400"/>
+        <color rgb="FF000000"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -286,7 +412,7 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FF00B400"/>
+        <color rgb="FF000000"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -297,7 +423,7 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FF00B400"/>
+        <color rgb="FF000000"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -325,14 +451,14 @@
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
-      <t>-6.3%</t>
+      <t>-5%</t>
     </r>
     <r>
       <t>，快车响应率：</t>
     </r>
     <r>
       <rPr>
-        <color rgb="FF00B400"/>
+        <color rgb="FF000000"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -343,7 +469,7 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FF00B400"/>
+        <color rgb="FF000000"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -354,7 +480,7 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FF00B400"/>
+        <color rgb="FF000000"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -372,7 +498,7 @@
 3、7米6：
 单量：154，调幅：-6.3%
 4、13米：
-单量：754，调幅：-6.3%</t>
+单量：754，调幅：-5%</t>
   </si>
   <si>
     <r>
@@ -380,7 +506,7 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FF00B400"/>
+        <color rgb="FFFF3232"/>
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
@@ -504,7 +630,54 @@
         <sz val="10.0"/>
         <rFont val="宋体"/>
       </rPr>
-      <t>-6.3%</t>
+      <t>-5%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">由于统计周期导致单量偏差
+最大降幅：-27.273%
+最大降幅不一致原因：调价前命中起步价兜底，调价后命中真实起步价兜底，老起步价兜底换标为真实起步价兜底
+最小降幅：-0.015%
+最小降幅不一致原因：调价后命中单公里兜底
+降幅超过-20%, 数量:1, 占比:0.01%
+不一致率：572/14,405 = 3.97%
+-该调的没调（单量）：42
+-该调的没调（占比）：0.294%
+-降幅过大（单量）：9
+-降幅过大（占比）：0.065%
+-降幅过小（单量）：522
+-降幅过小（占比）：3.615%
+不一致原因：起步价兜底、单公里兜底
+</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">由于统计周期导致单量偏差
+最大降幅：-27.273%
+最大降幅不一致原因：调价前命中起步价兜底，调价后命中真实起步价兜底，老起步价兜底换标为真实起步价兜底
+最小降幅：-0.015%
+最小降幅不一致原因：调价后命中单公里兜底
+降幅超过-20%, 数量:1, 占比:0.01%
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FFD18B0C"/>
+        <sz val="10.0"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>不一致率：572/14,405 = 3.97%</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+-该调的没调（单量）：42
+-该调的没调（占比）：0.294%
+-降幅过大（单量）：9
+-降幅过大（占比）：0.065%
+-降幅过小（单量）：522
+-降幅过小（占比）：3.615%
+不一致原因：起步价兜底、单公里兜底
+</t>
     </r>
   </si>
 </sst>
@@ -513,7 +686,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="41">
+  <fonts count="53">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -528,17 +701,105 @@
     </font>
     <font>
       <name val="宋体"/>
+      <sz val="14.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10.0"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="18.0"/>
+      <b val="true"/>
+      <color rgb="FF00B400"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF00B400"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF00B400"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="14.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="18.0"/>
+      <b val="true"/>
+      <color rgb="FFD18B0C"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FFD18B0C"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FFD18B0C"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FFD18B0C"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="14.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="18.0"/>
+      <b val="true"/>
+      <color rgb="FFD18B0C"/>
+    </font>
+    <font>
+      <name val="宋体"/>
       <sz val="10.0"/>
       <color rgb="FFFF3232"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <sz val="10.0"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FFFF3232"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF00B400"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FFFF3232"/>
     </font>
     <font>
       <name val="宋体"/>
@@ -548,16 +809,141 @@
     <font>
       <name val="宋体"/>
       <sz val="10.0"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF00B400"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FFFF3232"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF00B400"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF00B400"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FFFF3232"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF00B400"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FFFF3232"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FFFF3232"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF00B400"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FFFF3232"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
       <color rgb="FFD18B0C"/>
     </font>
     <font>
       <name val="宋体"/>
       <sz val="10.0"/>
+      <color rgb="FF00B400"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
       <color rgb="FFFF3232"/>
     </font>
     <font>
       <name val="宋体"/>
       <sz val="10.0"/>
+      <color rgb="FF00B400"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
+      <color rgb="FF00B400"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="10.0"/>
       <color rgb="FFFF3232"/>
     </font>
     <font>
@@ -568,157 +954,7 @@
     <font>
       <name val="宋体"/>
       <sz val="10.0"/>
-      <color rgb="FFFF3232"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
       <color rgb="FFD18B0C"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FFFF3232"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FFFF3232"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FFFF3232"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FFFF3232"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FFD18B0C"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FFFF3232"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FFFF3232"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="10.0"/>
-      <color rgb="FF00B400"/>
     </font>
   </fonts>
   <fills count="4">
@@ -811,11 +1047,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyAlignment="true" applyBorder="true" applyFill="true" applyFont="true">
       <alignment horizontal="center" wrapText="true" vertical="center"/>
       <protection locked="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" wrapText="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="left" wrapText="true" vertical="top"/>
@@ -826,11 +1065,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="80.0" customWidth="true"/>
-    <col min="2" max="2" width="80.0" customWidth="true"/>
+    <col min="1" max="1" width="15.0" customWidth="true"/>
+    <col min="2" max="2" width="20.0" customWidth="true"/>
+    <col min="3" max="3" width="12.0" customWidth="true"/>
+    <col min="4" max="4" width="70.0" customWidth="true"/>
+    <col min="5" max="5" width="50.0" customWidth="true"/>
+    <col min="6" max="6" width="60.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -840,32 +1083,83 @@
       <c r="B1" t="s" s="1">
         <v>1</v>
       </c>
+      <c r="C1" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s" s="3">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s" s="3">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s" s="3">
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>9</v>
+        <v>18</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s" s="3">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s" s="3">
+        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="F4" t="s" s="3">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A4"/>
+  </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>